--- a/EKG_Kalite_Yönetim_Sistemi/12_Üretim ve Malzeme Akış Yönetimi/01_MMFM1 - Planlama ve İzlenebilirlik/EKG-LOJ-PRS-04_izlenebilirlik_proseduru_ve_tatbikat_kaydi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/12_Üretim ve Malzeme Akış Yönetimi/01_MMFM1 - Planlama ve İzlenebilirlik/EKG-LOJ-PRS-04_izlenebilirlik_proseduru_ve_tatbikat_kaydi.xlsx
@@ -754,7 +754,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-PRS-04&amp;C&amp;"Arial,Regular"&amp;11İzlenebilirlik Prosedürü ve Tatbikat Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 13.05.2026 | Revizyon: 12.08.2026
+Revizyon nedeni: Çift yönlü izlenebilirlik ve miktar zinciri düzeltildi; kimyasal hesap kapsamı açıklanıp boş sekme kaldırıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -925,7 +926,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-PRS-04&amp;C&amp;"Arial,Regular"&amp;11İzlenebilirlik Prosedürü ve Tatbikat Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 13.05.2026 | Revizyon: 12.08.2026
+Revizyon nedeni: Çift yönlü izlenebilirlik ve miktar zinciri düzeltildi; kimyasal hesap kapsamı açıklanıp boş sekme kaldırıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>